--- a/src/main/resources/static/template_exel/caisse/template_import_caisse.xlsx
+++ b/src/main/resources/static/template_exel/caisse/template_import_caisse.xlsx
@@ -3,19 +3,107 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
   <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
+  <sheets>
+    <sheet sheetId="1" name="Caisse" state="visible" r:id="rId4"/>
+  </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="25">
+  <si>
+    <t>dateMouvement</t>
+  </si>
+  <si>
+    <t>typeMouvement</t>
+  </si>
+  <si>
+    <t>montant</t>
+  </si>
+  <si>
+    <t>2026-01-15</t>
+  </si>
+  <si>
+    <t>Entree</t>
+  </si>
+  <si>
+    <t>45000.000</t>
+  </si>
+  <si>
+    <t>2026-01-20</t>
+  </si>
+  <si>
+    <t>Sortie</t>
+  </si>
+  <si>
+    <t>12000.500</t>
+  </si>
+  <si>
+    <t>2026-02-01</t>
+  </si>
+  <si>
+    <t>78000.000</t>
+  </si>
+  <si>
+    <t>2026-02-14</t>
+  </si>
+  <si>
+    <t>5600.750</t>
+  </si>
+  <si>
+    <t>2026-03-10</t>
+  </si>
+  <si>
+    <t>32000.000</t>
+  </si>
+  <si>
+    <t>2026-03-25</t>
+  </si>
+  <si>
+    <t>8900.000</t>
+  </si>
+  <si>
+    <t>2026-04-05</t>
+  </si>
+  <si>
+    <t>150000.000</t>
+  </si>
+  <si>
+    <t>2026-04-18</t>
+  </si>
+  <si>
+    <t>22300.000</t>
+  </si>
+  <si>
+    <t>2026-05-01</t>
+  </si>
+  <si>
+    <t>95000.000</t>
+  </si>
+  <si>
+    <t>2026-05-12</t>
+  </si>
+  <si>
+    <t>4310.250</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
       <scheme val="minor"/>
       <sz val="11"/>
       <name val="Calibri"/>
+    </font>
+    <font>
+      <color rgb="FF2C3E50"/>
+      <sz val="8"/>
+      <name val="Arial"/>
     </font>
   </fonts>
   <fills count="2">
@@ -38,8 +126,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="bottom"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -375,4 +466,139 @@
   </a:objectDefaults>
   <a:extraClrSchemeLst/>
 </a:theme>
+</file>
+
+<file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:C11"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="24" width="13.571428571428571" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A8" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A9" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A10" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A11" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+</worksheet>
 </file>